--- a/prop/translation/teleoperation-network.xlsx
+++ b/prop/translation/teleoperation-network.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>English Name (英文名称)</t>
   </si>
@@ -287,7 +287,7 @@
     <t>For equipment maintenance, inspection, assembly, and complex workstation assistance, enabling high-quality operations with reduced on-site manpower.</t>
   </si>
   <si>
-    <t>面向设备检修、自动化装配及复杂工位辅助等高精度任务，有效精简现场人力，同时显著提升作业的一致性与安全性</t>
+    <t>面向设备检修、自动化装配及复杂工位辅助等任务，有效精简现场人力，同时显著提升作业的一致性与安全性</t>
   </si>
   <si>
     <t>Manufacturing / Mining / Construction / Logistics</t>
@@ -323,7 +323,7 @@
     <t>Supports exception handling, routine operational assistance, and service execution in commercial environments, improving service continuity and operational efficiency.</t>
   </si>
   <si>
-    <t>支持商业场景下的异常实时处置、日常导览与精细化服务，保障业务连续性并优化运营效率</t>
+    <t>支持商业场景下的日常导览、精细化服务与异常实时处置，优化运营效率</t>
   </si>
   <si>
     <t>Retail / Hospitality / Healthcare / Logistics</t>
@@ -341,6 +341,9 @@
     <t>Designed for assistive services, daily support, and companionship-oriented tasks, creating a remote enablement path for future home robotics.</t>
   </si>
   <si>
+    <t>面向辅助服务、日常支持与陪护场景，为未来家用机器人的远程赋能开启新路径</t>
+  </si>
+  <si>
     <t>Elderly Care / Daily Assistance / Companionship / Rehabilitation</t>
   </si>
   <si>
@@ -356,7 +359,7 @@
     <t>Captures demonstration data, interaction data, and environmental feedback from real teleoperation workflows, accelerating model training and intelligence upgrades.</t>
   </si>
   <si>
-    <t>基于真实遥操作工作流，精准捕捉专家级示范数据与环境反馈，驱动具身大模型的训练与认知升级</t>
+    <t>基于真实遥操作工作流，精准捕捉专家级示范数据与环境反馈，驱动具身大模型的迭代升级</t>
   </si>
   <si>
     <t>Demonstration / Simulation / Annotation / Model Iteration</t>
@@ -1818,39 +1821,39 @@
         <v>102</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1" spans="1:2">
       <c r="A53" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:2">
       <c r="A54" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" ht="54" customHeight="1" spans="1:2">
       <c r="A55" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1" spans="1:2">
       <c r="A56" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
